--- a/mobile/src/ElectronicLogbook.Mobile/Templates/LogbookExportFull.xlsx
+++ b/mobile/src/ElectronicLogbook.Mobile/Templates/LogbookExportFull.xlsx
@@ -916,141 +916,103 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellXfs count="122">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
       <extLst>
@@ -1059,17 +1021,23 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1092,7 +1060,7 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1103,9 +1071,6 @@
     </xf>
     <xf numFmtId="170" fontId="6" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="172" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1125,13 +1090,13 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1152,17 +1117,6 @@
     <xf numFmtId="165" fontId="8" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1175,28 +1129,6 @@
     <xf numFmtId="166" fontId="7" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1311,11 +1243,170 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="131">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1340,6 +1431,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1354,6 +1446,33 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1378,6 +1497,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1392,6 +1512,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1416,6 +1565,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1430,6 +1580,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1454,6 +1633,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1468,6 +1648,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1492,6 +1701,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1506,6 +1716,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1530,7 +1769,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1545,6 +1784,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1569,6 +1837,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1583,6 +1852,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1607,6 +1905,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1621,6 +1920,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1645,6 +1973,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1659,6 +1988,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1683,6 +2041,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1697,6 +2056,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1721,6 +2109,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1735,6 +2124,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1759,6 +2177,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1773,6 +2192,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1797,6 +2245,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1811,6 +2260,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1835,6 +2313,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1849,6 +2328,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1873,6 +2381,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1887,6 +2396,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1912,7 +2450,7 @@
           <bgColor rgb="FF333333"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1927,6 +2465,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="169" formatCode="0;;;@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1971,25 +2538,17 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1998,13 +2557,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2051,26 +2607,17 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2078,13 +2625,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2131,26 +2675,17 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2158,13 +2693,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2211,26 +2743,17 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2238,13 +2761,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2291,6 +2811,34 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -2325,6 +2873,306 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2371,26 +3219,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2398,13 +3238,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2451,26 +3288,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2478,13 +3307,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2531,26 +3357,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2558,13 +3376,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2611,26 +3426,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2638,13 +3445,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2691,26 +3495,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2718,13 +3514,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2771,26 +3564,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2798,13 +3583,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2851,26 +3633,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2878,13 +3652,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2931,6 +3702,35 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -2965,6 +3765,518 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3011,26 +4323,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -3038,13 +4342,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3091,6 +4392,35 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -3125,6 +4455,104 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3164,6 +4592,41 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
       <font>
@@ -3217,6 +4680,41 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -3244,6 +4742,39 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
       <font>
@@ -3401,6 +4932,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -3432,6 +4993,34 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3465,6 +5054,34 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3496,6 +5113,36 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3541,6 +5188,34 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -3572,6 +5247,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="dd"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3618,6 +5322,35 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="d"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -3652,6 +5385,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3698,6 +5460,39 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -3732,6 +5527,41 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3756,6 +5586,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -3784,1821 +5615,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="169" formatCode="0;;;@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="dd"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="d"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
@@ -5763,105 +5780,105 @@
     <sortCondition ref="C6"/>
   </sortState>
   <tableColumns count="63">
-    <tableColumn id="56" xr3:uid="{D480B3D9-F0FD-4EFA-B700-B58C42026787}" name="EntryID" dataDxfId="125" totalsRowDxfId="62"/>
-    <tableColumn id="1" xr3:uid="{4A9F7973-DB93-445C-A438-9DA51DE4C8E6}" name="Date" dataDxfId="124" totalsRowDxfId="61">
+    <tableColumn id="56" xr3:uid="{D480B3D9-F0FD-4EFA-B700-B58C42026787}" name="EntryID" dataDxfId="125" totalsRowDxfId="124"/>
+    <tableColumn id="1" xr3:uid="{4A9F7973-DB93-445C-A438-9DA51DE4C8E6}" name="Date" dataDxfId="123" totalsRowDxfId="122">
       <calculatedColumnFormula>IFERROR(IF(DAY(DATE(Logbook[[#This Row],[Year]],IF(ISNUMBER(Logbook[[#This Row],[Month]]),MONTH(Logbook[[#This Row],[Month]]),MONTH(DATEVALUE(Logbook[[#This Row],[Month]]&amp;" 1"))),IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]]))))&lt;&gt;IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]])),NA(),DATE(Logbook[[#This Row],[Year]],IF(ISNUMBER(Logbook[[#This Row],[Month]]),MONTH(Logbook[[#This Row],[Month]]),MONTH(DATEVALUE(Logbook[[#This Row],[Month]]&amp;" 1"))),IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]])))),NA())</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{5DE4E2FA-DD37-47CC-B3B2-F1F7CE60F8EF}" name="Year" dataDxfId="123" totalsRowDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{7F2FD0DE-1EBD-4A25-9AB2-8B2FD2016437}" name="Month" dataDxfId="122" totalsRowDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{C1637A1C-51D7-4EF1-B132-362CD3F92571}" name="Day" dataDxfId="121" totalsRowDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{96485EE2-5F0F-4FA0-B939-E32C66C44C7A}" name="Type" dataDxfId="120" totalsRowDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{4F0FBA5D-D369-4B9F-89AE-FEDEFC370AFE}" name="Reg" dataDxfId="119" totalsRowDxfId="56"/>
-    <tableColumn id="59" xr3:uid="{08CD5548-8146-40A6-94B9-0F79712B2ABF}" name="Flight ID" dataDxfId="118" totalsRowDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{0E4DB6A7-0018-4A8F-AFD7-61529B568497}" name="PIC" totalsRowLabel="Grand Total Flying Hours" dataDxfId="117" totalsRowDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{7D9307E7-1F1E-42B0-9A4E-D7903D4B651E}" name="Other Pilot or Crew" totalsRowFunction="custom" dataDxfId="116" totalsRowDxfId="53">
+    <tableColumn id="53" xr3:uid="{5DE4E2FA-DD37-47CC-B3B2-F1F7CE60F8EF}" name="Year" dataDxfId="121" totalsRowDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{7F2FD0DE-1EBD-4A25-9AB2-8B2FD2016437}" name="Month" dataDxfId="119" totalsRowDxfId="118"/>
+    <tableColumn id="3" xr3:uid="{C1637A1C-51D7-4EF1-B132-362CD3F92571}" name="Day" dataDxfId="117" totalsRowDxfId="116"/>
+    <tableColumn id="4" xr3:uid="{96485EE2-5F0F-4FA0-B939-E32C66C44C7A}" name="Type" dataDxfId="115" totalsRowDxfId="114"/>
+    <tableColumn id="5" xr3:uid="{4F0FBA5D-D369-4B9F-89AE-FEDEFC370AFE}" name="Reg" dataDxfId="113" totalsRowDxfId="112"/>
+    <tableColumn id="59" xr3:uid="{08CD5548-8146-40A6-94B9-0F79712B2ABF}" name="Flight ID" dataDxfId="111" totalsRowDxfId="110"/>
+    <tableColumn id="6" xr3:uid="{0E4DB6A7-0018-4A8F-AFD7-61529B568497}" name="PIC" totalsRowLabel="Grand Total Flying Hours" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="7" xr3:uid="{7D9307E7-1F1E-42B0-9A4E-D7903D4B651E}" name="Other Pilot or Crew" totalsRowFunction="custom" dataDxfId="107" totalsRowDxfId="106">
       <totalsRowFormula>SUBTOTAL(109,Logbook[TotalHours])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="62" xr3:uid="{35D88777-AA03-4EF0-B227-9E2048B1AA5E}" name="From" dataDxfId="115" totalsRowDxfId="52"/>
-    <tableColumn id="60" xr3:uid="{7742768E-54CE-4898-B717-E41D101B8D07}" name="To" dataDxfId="114" totalsRowDxfId="51"/>
-    <tableColumn id="64" xr3:uid="{8831D28C-8B2A-4FCF-A3EC-8584D90657FE}" name="Via" dataDxfId="113" totalsRowDxfId="50"/>
-    <tableColumn id="63" xr3:uid="{51D1410F-0100-42EB-81DF-35978C12F28B}" name="Remarks" dataDxfId="112" totalsRowDxfId="49"/>
-    <tableColumn id="58" xr3:uid="{15C88657-9674-4D76-90C3-DC868F8A7B1B}" name="FR" dataDxfId="111" totalsRowDxfId="48"/>
-    <tableColumn id="38" xr3:uid="{17B82195-E8EA-4688-97B0-F2E1AD927F10}" name="IPC" dataDxfId="110" totalsRowDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{50C057AA-9B70-4B51-A37B-5531F77284BF}" name="OPC" totalsRowLabel="TOTALS:" dataDxfId="109" totalsRowDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{C53B3FE9-B5B3-4FE4-9D2F-CC5CB5F157FB}" name="Custom 1" totalsRowFunction="sum" dataDxfId="108" totalsRowDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{D4DF1EA3-5D43-434F-AEBE-A605D9FFD457}" name="Custom 2" totalsRowFunction="sum" dataDxfId="107" totalsRowDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{741C7510-6E1A-49A3-9C9E-E42097510CEC}" name="Custom 3" totalsRowFunction="sum" dataDxfId="106" totalsRowDxfId="43"/>
-    <tableColumn id="57" xr3:uid="{4E4B2A2B-F980-49E5-9F31-D9E96FB9A587}" name="Custom 4" totalsRowFunction="sum" dataDxfId="105" totalsRowDxfId="42"/>
-    <tableColumn id="12" xr3:uid="{EC4A1A18-0A2D-49AC-BFCD-E01030F64888}" name="SeIcusDay" totalsRowFunction="sum" dataDxfId="104" totalsRowDxfId="41"/>
-    <tableColumn id="13" xr3:uid="{40EA09A9-61CC-4653-B74B-0553995DCA63}" name="SeIcusNight" totalsRowFunction="sum" dataDxfId="103" totalsRowDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{482A4ED7-9580-4817-A603-06ECE9BF848E}" name="SeDualDay" totalsRowFunction="sum" dataDxfId="102" totalsRowDxfId="39"/>
-    <tableColumn id="15" xr3:uid="{ECD3AC03-3033-4736-ACF4-108BA4CADCA9}" name="SeDualNight" totalsRowFunction="sum" dataDxfId="101" totalsRowDxfId="38"/>
-    <tableColumn id="16" xr3:uid="{0D5B8F94-E65D-4CF8-BCFB-AB7B435439E4}" name="SeCommandDay" totalsRowFunction="sum" dataDxfId="100" totalsRowDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{4A01EC43-EE14-4A57-8790-63AD1C10441E}" name="SeCommandNight" totalsRowFunction="sum" dataDxfId="99" totalsRowDxfId="36"/>
-    <tableColumn id="18" xr3:uid="{A2239AA3-C2C3-451B-A2A2-60C04EDEE6F8}" name="MeIcusDay" totalsRowFunction="sum" dataDxfId="98" totalsRowDxfId="35"/>
-    <tableColumn id="19" xr3:uid="{ECBDA53E-F388-4471-8A51-D64F6CA99F19}" name="MeIcusNight" totalsRowFunction="sum" dataDxfId="97" totalsRowDxfId="34"/>
-    <tableColumn id="20" xr3:uid="{27DA3BE1-5062-4E05-9011-130B57ABC06D}" name="MeDualDay" totalsRowFunction="sum" dataDxfId="96" totalsRowDxfId="33"/>
-    <tableColumn id="21" xr3:uid="{29820283-7307-4F78-B87D-C36611B4DDD3}" name="MeDualNight" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="32"/>
-    <tableColumn id="22" xr3:uid="{152C87A1-34A8-4A96-8523-01A7DF8751C5}" name="MeCommandDay" totalsRowFunction="sum" dataDxfId="94" totalsRowDxfId="31"/>
-    <tableColumn id="23" xr3:uid="{61E0C9F1-CFD0-42E5-A7DC-2C41309F344C}" name="MeCommandNight" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="30"/>
-    <tableColumn id="24" xr3:uid="{ADC4E9A8-C2BB-4203-AD5D-C0E8E6DD1FEF}" name="CopilotDay" totalsRowFunction="sum" dataDxfId="92" totalsRowDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{FAA08A34-D45C-4AB5-83C7-9DB2A8B0C2E3}" name="CopilotNight" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="28"/>
-    <tableColumn id="26" xr3:uid="{2C960429-5AF1-4AB6-A6DC-6DA0D3E44FE8}" name="IfrIf" totalsRowFunction="sum" dataDxfId="90" totalsRowDxfId="27"/>
-    <tableColumn id="27" xr3:uid="{FADE530A-F0C4-4ADF-96CA-8E4406906F48}" name="IfrSim" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="26"/>
-    <tableColumn id="28" xr3:uid="{1ABCF964-1A5D-4D44-94AD-A0AEA9405B55}" name="LandingsDay" totalsRowFunction="sum" dataDxfId="88" totalsRowDxfId="25"/>
-    <tableColumn id="29" xr3:uid="{402C33EC-355B-4E27-9EDC-61E77D1949DA}" name="LandingsNight" totalsRowFunction="sum" dataDxfId="87" totalsRowDxfId="24"/>
-    <tableColumn id="30" xr3:uid="{B49D717E-472F-4145-9125-1A5E9E338FAD}" name="ILS" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="23"/>
-    <tableColumn id="31" xr3:uid="{3D63FAA1-0E05-4BEC-9D6B-6D9D19465958}" name="VOR" totalsRowFunction="sum" dataDxfId="85" totalsRowDxfId="22"/>
-    <tableColumn id="32" xr3:uid="{00BE2531-4BA9-460D-B922-80C609F07A18}" name="RNP" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="21"/>
-    <tableColumn id="33" xr3:uid="{DCC3F16C-616F-41F1-BA39-755856D47AF1}" name="NDB" totalsRowFunction="sum" dataDxfId="83" totalsRowDxfId="20"/>
-    <tableColumn id="34" xr3:uid="{19FB5B5C-450E-4FCD-B6AD-F55217E6EEFE}" name="DGA (CDI)" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="19"/>
-    <tableColumn id="35" xr3:uid="{6D9A8927-28A8-42D9-8C00-39BDAD87B064}" name="DGA (Azi)" totalsRowFunction="sum" dataDxfId="81" totalsRowDxfId="18"/>
-    <tableColumn id="36" xr3:uid="{F52CFC91-2462-4865-A135-E24F1A59D2F9}" name="Circling" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="17"/>
-    <tableColumn id="54" xr3:uid="{FA8413FA-CA54-4EB0-A142-59A7B4A9BE3A}" name="TotalHours" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="16">
+    <tableColumn id="62" xr3:uid="{35D88777-AA03-4EF0-B227-9E2048B1AA5E}" name="From" dataDxfId="105" totalsRowDxfId="104"/>
+    <tableColumn id="60" xr3:uid="{7742768E-54CE-4898-B717-E41D101B8D07}" name="To" dataDxfId="2" totalsRowDxfId="103"/>
+    <tableColumn id="64" xr3:uid="{8831D28C-8B2A-4FCF-A3EC-8584D90657FE}" name="Via" dataDxfId="0" totalsRowDxfId="102"/>
+    <tableColumn id="63" xr3:uid="{51D1410F-0100-42EB-81DF-35978C12F28B}" name="Remarks" dataDxfId="1" totalsRowDxfId="101"/>
+    <tableColumn id="58" xr3:uid="{15C88657-9674-4D76-90C3-DC868F8A7B1B}" name="FR" dataDxfId="100" totalsRowDxfId="99"/>
+    <tableColumn id="38" xr3:uid="{17B82195-E8EA-4688-97B0-F2E1AD927F10}" name="IPC" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="8" xr3:uid="{50C057AA-9B70-4B51-A37B-5531F77284BF}" name="OPC" totalsRowLabel="TOTALS:" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="9" xr3:uid="{C53B3FE9-B5B3-4FE4-9D2F-CC5CB5F157FB}" name="Custom 1" totalsRowFunction="sum" dataDxfId="94" totalsRowDxfId="93"/>
+    <tableColumn id="10" xr3:uid="{D4DF1EA3-5D43-434F-AEBE-A605D9FFD457}" name="Custom 2" totalsRowFunction="sum" dataDxfId="92" totalsRowDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{741C7510-6E1A-49A3-9C9E-E42097510CEC}" name="Custom 3" totalsRowFunction="sum" dataDxfId="90" totalsRowDxfId="89"/>
+    <tableColumn id="57" xr3:uid="{4E4B2A2B-F980-49E5-9F31-D9E96FB9A587}" name="Custom 4" totalsRowFunction="sum" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="12" xr3:uid="{EC4A1A18-0A2D-49AC-BFCD-E01030F64888}" name="SeIcusDay" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="13" xr3:uid="{40EA09A9-61CC-4653-B74B-0553995DCA63}" name="SeIcusNight" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{482A4ED7-9580-4817-A603-06ECE9BF848E}" name="SeDualDay" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="15" xr3:uid="{ECD3AC03-3033-4736-ACF4-108BA4CADCA9}" name="SeDualNight" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="16" xr3:uid="{0D5B8F94-E65D-4CF8-BCFB-AB7B435439E4}" name="SeCommandDay" totalsRowFunction="sum" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="17" xr3:uid="{4A01EC43-EE14-4A57-8790-63AD1C10441E}" name="SeCommandNight" totalsRowFunction="sum" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="18" xr3:uid="{A2239AA3-C2C3-451B-A2A2-60C04EDEE6F8}" name="MeIcusDay" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="19" xr3:uid="{ECBDA53E-F388-4471-8A51-D64F6CA99F19}" name="MeIcusNight" totalsRowFunction="sum" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="20" xr3:uid="{27DA3BE1-5062-4E05-9011-130B57ABC06D}" name="MeDualDay" totalsRowFunction="sum" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="21" xr3:uid="{29820283-7307-4F78-B87D-C36611B4DDD3}" name="MeDualNight" totalsRowFunction="sum" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="22" xr3:uid="{152C87A1-34A8-4A96-8523-01A7DF8751C5}" name="MeCommandDay" totalsRowFunction="sum" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="23" xr3:uid="{61E0C9F1-CFD0-42E5-A7DC-2C41309F344C}" name="MeCommandNight" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="24" xr3:uid="{ADC4E9A8-C2BB-4203-AD5D-C0E8E6DD1FEF}" name="CopilotDay" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="25" xr3:uid="{FAA08A34-D45C-4AB5-83C7-9DB2A8B0C2E3}" name="CopilotNight" totalsRowFunction="sum" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="26" xr3:uid="{2C960429-5AF1-4AB6-A6DC-6DA0D3E44FE8}" name="IfrIf" totalsRowFunction="sum" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="27" xr3:uid="{FADE530A-F0C4-4ADF-96CA-8E4406906F48}" name="IfrSim" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="28" xr3:uid="{1ABCF964-1A5D-4D44-94AD-A0AEA9405B55}" name="LandingsDay" totalsRowFunction="sum" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="29" xr3:uid="{402C33EC-355B-4E27-9EDC-61E77D1949DA}" name="LandingsNight" totalsRowFunction="sum" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="30" xr3:uid="{B49D717E-472F-4145-9125-1A5E9E338FAD}" name="ILS" totalsRowFunction="sum" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="31" xr3:uid="{3D63FAA1-0E05-4BEC-9D6B-6D9D19465958}" name="VOR" totalsRowFunction="sum" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="32" xr3:uid="{00BE2531-4BA9-460D-B922-80C609F07A18}" name="RNP" totalsRowFunction="sum" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="33" xr3:uid="{DCC3F16C-616F-41F1-BA39-755856D47AF1}" name="NDB" totalsRowFunction="sum" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="34" xr3:uid="{19FB5B5C-450E-4FCD-B6AD-F55217E6EEFE}" name="DGA (CDI)" totalsRowFunction="sum" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="35" xr3:uid="{6D9A8927-28A8-42D9-8C00-39BDAD87B064}" name="DGA (Azi)" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="36" xr3:uid="{F52CFC91-2462-4865-A135-E24F1A59D2F9}" name="Circling" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="54" xr3:uid="{FA8413FA-CA54-4EB0-A142-59A7B4A9BE3A}" name="TotalHours" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
       <calculatedColumnFormula>SUM(Logbook[[#This Row],[SeIcusDay]:[CopilotNight]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{6F315B7F-6161-4654-A259-C403C03FD38C}" name="TotalApps" totalsRowFunction="sum" dataDxfId="78" totalsRowDxfId="15">
+    <tableColumn id="37" xr3:uid="{6F315B7F-6161-4654-A259-C403C03FD38C}" name="TotalApps" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
       <calculatedColumnFormula>SUM(Logbook[[#This Row],[ILS]:[DGA (Azi)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{FC445918-ECBA-41EC-A2CD-AAD3627DAC1A}" name="CumLandingsDay" dataDxfId="77" totalsRowDxfId="14">
+    <tableColumn id="39" xr3:uid="{FC445918-ECBA-41EC-A2CD-AAD3627DAC1A}" name="CumLandingsDay" dataDxfId="32" totalsRowDxfId="31">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumLandingsDay]),Logbook[[#This Row],[LandingsDay]],Logbook[[#This Row],[LandingsDay]]+INDEX(Logbook[CumLandingsDay],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{7EDEE77D-C37A-462D-A6BA-2FE217273635}" name="CumLandingsNight" dataDxfId="76" totalsRowDxfId="13">
+    <tableColumn id="40" xr3:uid="{7EDEE77D-C37A-462D-A6BA-2FE217273635}" name="CumLandingsNight" dataDxfId="30" totalsRowDxfId="29">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumLandingsNight]),Logbook[[#This Row],[LandingsNight]],Logbook[[#This Row],[LandingsNight]]+INDEX(Logbook[CumLandingsNight],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{26B7EE4D-23EF-49CC-B3B7-76C866CA9AB5}" name="CumILS" dataDxfId="75" totalsRowDxfId="12">
+    <tableColumn id="41" xr3:uid="{26B7EE4D-23EF-49CC-B3B7-76C866CA9AB5}" name="CumILS" dataDxfId="28" totalsRowDxfId="27">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumILS]),Logbook[[#This Row],[ILS]],Logbook[[#This Row],[ILS]]+INDEX(Logbook[CumILS],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{535B9677-818A-48BF-95F1-87A2ED8DAC0E}" name="CumVOR" dataDxfId="74" totalsRowDxfId="11">
+    <tableColumn id="42" xr3:uid="{535B9677-818A-48BF-95F1-87A2ED8DAC0E}" name="CumVOR" dataDxfId="26" totalsRowDxfId="25">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumVOR]),Logbook[[#This Row],[VOR]],Logbook[[#This Row],[VOR]]+INDEX(Logbook[CumVOR],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{144757E6-C50D-4123-B1DB-42C7FF7BA87A}" name="CumRNP" dataDxfId="73" totalsRowDxfId="10">
+    <tableColumn id="43" xr3:uid="{144757E6-C50D-4123-B1DB-42C7FF7BA87A}" name="CumRNP" dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumRNP]),Logbook[[#This Row],[RNP]],Logbook[[#This Row],[RNP]]+INDEX(Logbook[CumRNP],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{73B414DB-72DC-4DDF-86A1-A0219BB39101}" name="CumNDB" dataDxfId="72" totalsRowDxfId="9">
+    <tableColumn id="44" xr3:uid="{73B414DB-72DC-4DDF-86A1-A0219BB39101}" name="CumNDB" dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumNDB]),Logbook[[#This Row],[NDB]],Logbook[[#This Row],[NDB]]+INDEX(Logbook[CumNDB],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{AFA0920F-834E-4312-94D5-1BB65D1BD529}" name="CumDgaCdi" dataDxfId="71" totalsRowDxfId="8">
+    <tableColumn id="45" xr3:uid="{AFA0920F-834E-4312-94D5-1BB65D1BD529}" name="CumDgaCdi" dataDxfId="20" totalsRowDxfId="19">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumDgaCdi]),Logbook[[#This Row],[DGA (CDI)]],Logbook[[#This Row],[DGA (CDI)]]+INDEX(Logbook[CumDgaCdi],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{DE0A8510-855B-4C7A-9DC5-4006EA854638}" name="CumDgaAzi" dataDxfId="70" totalsRowDxfId="7">
+    <tableColumn id="46" xr3:uid="{DE0A8510-855B-4C7A-9DC5-4006EA854638}" name="CumDgaAzi" dataDxfId="18" totalsRowDxfId="17">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumDgaAzi]),Logbook[[#This Row],[DGA (Azi)]],Logbook[[#This Row],[DGA (Azi)]]+INDEX(Logbook[CumDgaAzi],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="47" xr3:uid="{2E62ECFC-8938-43ED-A7A3-96021161E246}" name="CumCirc" dataDxfId="69" totalsRowDxfId="6">
+    <tableColumn id="47" xr3:uid="{2E62ECFC-8938-43ED-A7A3-96021161E246}" name="CumCirc" dataDxfId="16" totalsRowDxfId="15">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumCirc]),Logbook[[#This Row],[Circling]],Logbook[[#This Row],[Circling]]+INDEX(Logbook[CumCirc],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{27CD4B83-2190-43DC-845B-C2367A3B9709}" name="CumTotalApps" dataDxfId="68" totalsRowDxfId="5">
+    <tableColumn id="48" xr3:uid="{27CD4B83-2190-43DC-845B-C2367A3B9709}" name="CumTotalApps" dataDxfId="14" totalsRowDxfId="13">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumTotalApps]),Logbook[[#This Row],[TotalApps]],Logbook[[#This Row],[TotalApps]]+INDEX(Logbook[CumTotalApps],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="49" xr3:uid="{194F9066-B2DA-4EC2-9D85-921E960CF0B3}" name="CumTotalHours" dataDxfId="67" totalsRowDxfId="4">
+    <tableColumn id="49" xr3:uid="{194F9066-B2DA-4EC2-9D85-921E960CF0B3}" name="CumTotalHours" dataDxfId="12" totalsRowDxfId="11">
       <calculatedColumnFormula>SUM(INDEX(Logbook[TotalHours],1):Logbook[[#This Row],[TotalHours]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="50" xr3:uid="{D904A10A-DC61-4EF5-A0A7-8E4E66C716B2}" name="Cum2D" dataDxfId="66" totalsRowDxfId="3">
+    <tableColumn id="50" xr3:uid="{D904A10A-DC61-4EF5-A0A7-8E4E66C716B2}" name="Cum2D" dataDxfId="10" totalsRowDxfId="9">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[Cum2D]),SUM(Logbook[[#This Row],[VOR]:[DGA (Azi)]]),SUM(Logbook[[#This Row],[VOR]:[DGA (Azi)]])+INDEX(Logbook[Cum2D],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="51" xr3:uid="{53B0F290-2D6B-4939-856F-DDDAEF901884}" name="Cum3D" dataDxfId="65" totalsRowDxfId="2">
+    <tableColumn id="51" xr3:uid="{53B0F290-2D6B-4939-856F-DDDAEF901884}" name="Cum3D" dataDxfId="8" totalsRowDxfId="7">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[Cum3D]),Logbook[[#This Row],[ILS]],Logbook[[#This Row],[ILS]]+INDEX(Logbook[Cum3D],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{2B647697-03EA-4F4D-93DD-5D0A77657840}" name="CumCDI" dataDxfId="64" totalsRowDxfId="1">
+    <tableColumn id="52" xr3:uid="{2B647697-03EA-4F4D-93DD-5D0A77657840}" name="CumCDI" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumCDI]),SUM(Logbook[[#This Row],[ILS]:[RNP]])+Logbook[[#This Row],[DGA (CDI)]],SUM(Logbook[[#This Row],[ILS]:[RNP]])+Logbook[[#This Row],[DGA (CDI)]]+INDEX(Logbook[CumCDI],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="55" xr3:uid="{18C8F4D1-667B-429B-9365-8A96E578D433}" name="CumAzi" dataDxfId="63" totalsRowDxfId="0">
+    <tableColumn id="55" xr3:uid="{18C8F4D1-667B-429B-9365-8A96E578D433}" name="CumAzi" dataDxfId="4" totalsRowDxfId="3">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumAzi]),Logbook[[#This Row],[NDB]]+Logbook[[#This Row],[DGA (Azi)]],Logbook[[#This Row],[NDB]]+Logbook[[#This Row],[DGA (Azi)]]+INDEX(Logbook[CumAzi],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6172,48 +6189,48 @@
   <dimension ref="A1:BV104"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="38" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="38" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="39" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="40" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="41" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="42" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" style="38" customWidth="1"/>
-    <col min="9" max="9" width="13" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" style="38" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" style="38" customWidth="1"/>
-    <col min="14" max="15" width="35.7109375" style="38" customWidth="1"/>
-    <col min="16" max="18" width="9.5703125" style="38" customWidth="1"/>
-    <col min="19" max="20" width="14.28515625" style="43" customWidth="1"/>
-    <col min="21" max="22" width="14.28515625" style="40" customWidth="1"/>
-    <col min="23" max="40" width="6.28515625" style="38" customWidth="1"/>
-    <col min="41" max="47" width="7.7109375" style="38" customWidth="1"/>
-    <col min="48" max="48" width="15.28515625" style="43" hidden="1" customWidth="1"/>
-    <col min="49" max="49" width="14.42578125" style="44" hidden="1" customWidth="1"/>
-    <col min="50" max="50" width="16.28515625" style="38" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="17.7109375" style="38" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="7.42578125" style="38" hidden="1" customWidth="1"/>
-    <col min="53" max="53" width="8.7109375" style="38" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="10.28515625" style="38" hidden="1" customWidth="1"/>
-    <col min="55" max="55" width="8.7109375" style="38" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="11.28515625" style="38" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="11" style="38" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="8.28515625" style="38" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="14" style="38" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="14.7109375" style="38" hidden="1" customWidth="1"/>
-    <col min="61" max="62" width="7.42578125" style="38" hidden="1" customWidth="1"/>
-    <col min="63" max="63" width="8" style="40" hidden="1" customWidth="1"/>
-    <col min="64" max="64" width="8.42578125" style="38" hidden="1" customWidth="1"/>
-    <col min="65" max="65" width="3.7109375" style="38" customWidth="1"/>
-    <col min="66" max="66" width="0" style="38" hidden="1" customWidth="1"/>
-    <col min="67" max="67" width="8" style="38" hidden="1" customWidth="1"/>
-    <col min="68" max="68" width="8.42578125" style="38" hidden="1" customWidth="1"/>
-    <col min="69" max="70" width="0" style="38" hidden="1" customWidth="1"/>
-    <col min="71" max="71" width="8.42578125" style="38" hidden="1" customWidth="1"/>
-    <col min="72" max="74" width="0" style="38" hidden="1" customWidth="1"/>
-    <col min="75" max="16384" width="9.28515625" style="38" hidden="1"/>
+    <col min="1" max="1" width="3.7109375" style="30" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="31" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="32" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="33" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" style="34" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" style="30" customWidth="1"/>
+    <col min="9" max="9" width="13" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="30" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="30" customWidth="1"/>
+    <col min="14" max="15" width="35.7109375" style="30" customWidth="1"/>
+    <col min="16" max="18" width="9.5703125" style="30" customWidth="1"/>
+    <col min="19" max="20" width="14.28515625" style="35" customWidth="1"/>
+    <col min="21" max="22" width="14.28515625" style="32" customWidth="1"/>
+    <col min="23" max="40" width="6.28515625" style="30" customWidth="1"/>
+    <col min="41" max="47" width="7.7109375" style="30" customWidth="1"/>
+    <col min="48" max="48" width="15.28515625" style="35" hidden="1" customWidth="1"/>
+    <col min="49" max="49" width="14.42578125" style="36" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="16.28515625" style="30" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="17.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="7.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="8.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="30" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="8.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="56" max="56" width="11.28515625" style="30" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="11" style="30" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="8.28515625" style="30" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="14" style="30" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="14.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="61" max="62" width="7.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="63" max="63" width="8" style="32" hidden="1" customWidth="1"/>
+    <col min="64" max="64" width="8.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="65" max="65" width="3.7109375" style="30" customWidth="1"/>
+    <col min="66" max="66" width="0" style="30" hidden="1" customWidth="1"/>
+    <col min="67" max="67" width="8" style="30" hidden="1" customWidth="1"/>
+    <col min="68" max="68" width="8.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="69" max="70" width="0" style="30" hidden="1" customWidth="1"/>
+    <col min="71" max="71" width="8.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="72" max="74" width="0" style="30" hidden="1" customWidth="1"/>
+    <col min="75" max="16384" width="9.28515625" style="30" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:74" x14ac:dyDescent="0.25">
@@ -6229,99 +6246,99 @@
       <c r="BU1"/>
       <c r="BV1"/>
     </row>
-    <row r="2" spans="1:74" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:74" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="105" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="96" t="s">
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="100"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="96" t="s">
+      <c r="H2" s="78"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="K2" s="97"/>
-      <c r="L2" s="100" t="s">
+      <c r="K2" s="75"/>
+      <c r="L2" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="97"/>
-      <c r="P2" s="82" t="s">
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="96" t="s">
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="T2" s="100"/>
-      <c r="U2" s="100"/>
-      <c r="V2" s="97"/>
-      <c r="W2" s="82" t="s">
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="75"/>
+      <c r="W2" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="X2" s="82"/>
-      <c r="Y2" s="82"/>
-      <c r="Z2" s="82"/>
-      <c r="AA2" s="82"/>
-      <c r="AB2" s="82"/>
-      <c r="AC2" s="82" t="s">
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="AD2" s="82"/>
-      <c r="AE2" s="82"/>
-      <c r="AF2" s="82"/>
-      <c r="AG2" s="82"/>
-      <c r="AH2" s="82"/>
-      <c r="AI2" s="96" t="s">
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="82" t="s">
+      <c r="AJ2" s="75"/>
+      <c r="AK2" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="AL2" s="82"/>
-      <c r="AM2" s="92" t="s">
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="93"/>
-      <c r="AO2" s="82" t="s">
+      <c r="AN2" s="71"/>
+      <c r="AO2" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="AP2" s="82"/>
-      <c r="AQ2" s="82"/>
-      <c r="AR2" s="82"/>
-      <c r="AS2" s="82"/>
-      <c r="AT2" s="82"/>
-      <c r="AU2" s="90"/>
-      <c r="AV2" s="84" t="s">
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
+      <c r="AR2" s="60"/>
+      <c r="AS2" s="60"/>
+      <c r="AT2" s="60"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="AW2" s="85"/>
-      <c r="AX2" s="114" t="s">
+      <c r="AW2" s="63"/>
+      <c r="AX2" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
-      <c r="BB2" s="115"/>
-      <c r="BC2" s="115"/>
-      <c r="BD2" s="115"/>
-      <c r="BE2" s="115"/>
-      <c r="BF2" s="115"/>
-      <c r="BG2" s="115"/>
-      <c r="BH2" s="115"/>
-      <c r="BI2" s="115"/>
-      <c r="BJ2" s="115"/>
-      <c r="BK2" s="115"/>
-      <c r="BL2" s="116"/>
+      <c r="AY2" s="93"/>
+      <c r="AZ2" s="93"/>
+      <c r="BA2" s="93"/>
+      <c r="BB2" s="93"/>
+      <c r="BC2" s="93"/>
+      <c r="BD2" s="93"/>
+      <c r="BE2" s="93"/>
+      <c r="BF2" s="93"/>
+      <c r="BG2" s="93"/>
+      <c r="BH2" s="93"/>
+      <c r="BI2" s="93"/>
+      <c r="BJ2" s="93"/>
+      <c r="BK2" s="93"/>
+      <c r="BL2" s="94"/>
       <c r="BM2"/>
       <c r="BN2"/>
       <c r="BO2"/>
@@ -6333,117 +6350,117 @@
       <c r="BU2"/>
       <c r="BV2"/>
     </row>
-    <row r="3" spans="1:74" s="45" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:74" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="101"/>
-      <c r="T3" s="102"/>
-      <c r="U3" s="102"/>
-      <c r="V3" s="103"/>
-      <c r="W3" s="83" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="X3" s="83"/>
-      <c r="Y3" s="83" t="s">
+      <c r="X3" s="61"/>
+      <c r="Y3" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="Z3" s="83"/>
-      <c r="AA3" s="83" t="s">
+      <c r="Z3" s="61"/>
+      <c r="AA3" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="AB3" s="83"/>
-      <c r="AC3" s="83" t="s">
+      <c r="AB3" s="61"/>
+      <c r="AC3" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="83"/>
-      <c r="AE3" s="83" t="s">
+      <c r="AD3" s="61"/>
+      <c r="AE3" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="AF3" s="83"/>
-      <c r="AG3" s="83" t="s">
+      <c r="AF3" s="61"/>
+      <c r="AG3" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="AH3" s="83"/>
-      <c r="AI3" s="98"/>
-      <c r="AJ3" s="99"/>
-      <c r="AK3" s="83" t="s">
+      <c r="AH3" s="61"/>
+      <c r="AI3" s="76"/>
+      <c r="AJ3" s="77"/>
+      <c r="AK3" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="83" t="s">
+      <c r="AL3" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AM3" s="94" t="s">
+      <c r="AM3" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="AN3" s="94" t="s">
+      <c r="AN3" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="83" t="s">
+      <c r="AO3" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="AP3" s="83" t="s">
+      <c r="AP3" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="AQ3" s="83" t="s">
+      <c r="AQ3" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="AR3" s="83" t="s">
+      <c r="AR3" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="AS3" s="83" t="s">
+      <c r="AS3" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="AT3" s="83" t="s">
+      <c r="AT3" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="AU3" s="91" t="s">
+      <c r="AU3" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="AV3" s="86"/>
-      <c r="AW3" s="87"/>
-      <c r="AX3" s="114" t="s">
+      <c r="AV3" s="64"/>
+      <c r="AW3" s="65"/>
+      <c r="AX3" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="AY3" s="116"/>
-      <c r="AZ3" s="114" t="s">
+      <c r="AY3" s="94"/>
+      <c r="AZ3" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="BA3" s="115"/>
-      <c r="BB3" s="115"/>
-      <c r="BC3" s="115"/>
-      <c r="BD3" s="115"/>
-      <c r="BE3" s="115"/>
-      <c r="BF3" s="116"/>
-      <c r="BG3" s="117" t="s">
+      <c r="BA3" s="93"/>
+      <c r="BB3" s="93"/>
+      <c r="BC3" s="93"/>
+      <c r="BD3" s="93"/>
+      <c r="BE3" s="93"/>
+      <c r="BF3" s="94"/>
+      <c r="BG3" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="BH3" s="118"/>
-      <c r="BI3" s="119" t="s">
+      <c r="BH3" s="96"/>
+      <c r="BI3" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="BJ3" s="119" t="s">
+      <c r="BJ3" s="97" t="s">
         <v>26</v>
       </c>
-      <c r="BK3" s="119" t="s">
+      <c r="BK3" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="BL3" s="113" t="s">
+      <c r="BL3" s="91" t="s">
         <v>28</v>
       </c>
       <c r="BM3"/>
@@ -6457,121 +6474,121 @@
       <c r="BU3"/>
       <c r="BV3"/>
     </row>
-    <row r="4" spans="1:74" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:74" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="48" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
-      <c r="N4" s="104"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="104"/>
-      <c r="U4" s="104"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="46" t="s">
+      <c r="E4" s="89"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="82"/>
+      <c r="U4" s="82"/>
+      <c r="V4" s="77"/>
+      <c r="W4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="X4" s="46" t="s">
+      <c r="X4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="Y4" s="46" t="s">
+      <c r="Y4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="Z4" s="46" t="s">
+      <c r="Z4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AA4" s="46" t="s">
+      <c r="AA4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="AB4" s="46" t="s">
+      <c r="AB4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AC4" s="46" t="s">
+      <c r="AC4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="AD4" s="46" t="s">
+      <c r="AD4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AE4" s="46" t="s">
+      <c r="AE4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="AF4" s="46" t="s">
+      <c r="AF4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AG4" s="46" t="s">
+      <c r="AG4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="AH4" s="46" t="s">
+      <c r="AH4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AI4" s="46" t="s">
+      <c r="AI4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="AJ4" s="46" t="s">
+      <c r="AJ4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AK4" s="83"/>
-      <c r="AL4" s="83"/>
-      <c r="AM4" s="95"/>
-      <c r="AN4" s="95"/>
-      <c r="AO4" s="83"/>
-      <c r="AP4" s="83"/>
-      <c r="AQ4" s="83"/>
-      <c r="AR4" s="83"/>
-      <c r="AS4" s="83"/>
-      <c r="AT4" s="83"/>
-      <c r="AU4" s="91"/>
-      <c r="AV4" s="88"/>
-      <c r="AW4" s="89"/>
-      <c r="AX4" s="47" t="s">
+      <c r="AK4" s="61"/>
+      <c r="AL4" s="61"/>
+      <c r="AM4" s="73"/>
+      <c r="AN4" s="73"/>
+      <c r="AO4" s="61"/>
+      <c r="AP4" s="61"/>
+      <c r="AQ4" s="61"/>
+      <c r="AR4" s="61"/>
+      <c r="AS4" s="61"/>
+      <c r="AT4" s="61"/>
+      <c r="AU4" s="69"/>
+      <c r="AV4" s="66"/>
+      <c r="AW4" s="67"/>
+      <c r="AX4" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="AY4" s="47" t="s">
+      <c r="AY4" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AZ4" s="47" t="s">
+      <c r="AZ4" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="BA4" s="47" t="s">
+      <c r="BA4" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="BB4" s="47" t="s">
+      <c r="BB4" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="BC4" s="47" t="s">
+      <c r="BC4" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="BD4" s="47" t="s">
+      <c r="BD4" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="BE4" s="47" t="s">
+      <c r="BE4" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="BF4" s="47" t="s">
+      <c r="BF4" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="99"/>
-      <c r="BI4" s="119"/>
-      <c r="BJ4" s="119"/>
-      <c r="BK4" s="119"/>
-      <c r="BL4" s="113"/>
+      <c r="BG4" s="76"/>
+      <c r="BH4" s="77"/>
+      <c r="BI4" s="97"/>
+      <c r="BJ4" s="97"/>
+      <c r="BK4" s="97"/>
+      <c r="BL4" s="91"/>
       <c r="BM4"/>
       <c r="BN4"/>
       <c r="BO4"/>
@@ -6583,195 +6600,195 @@
       <c r="BU4"/>
       <c r="BV4"/>
     </row>
-    <row r="5" spans="1:74" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:74" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="Q5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="R5" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="S5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="T5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="U5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V5" s="13" t="s">
+      <c r="V5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="W5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="X5" s="23" t="s">
+      <c r="X5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Y5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="Z5" s="23" t="s">
+      <c r="Z5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="AA5" s="23" t="s">
+      <c r="AA5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="AB5" s="23" t="s">
+      <c r="AB5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="AC5" s="23" t="s">
+      <c r="AC5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="AD5" s="23" t="s">
+      <c r="AD5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="AE5" s="23" t="s">
+      <c r="AE5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AF5" s="23" t="s">
+      <c r="AF5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AG5" s="23" t="s">
+      <c r="AG5" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="AH5" s="23" t="s">
+      <c r="AH5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="AI5" s="23" t="s">
+      <c r="AI5" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="AJ5" s="23" t="s">
+      <c r="AJ5" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="AK5" s="23" t="s">
+      <c r="AK5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="AL5" s="23" t="s">
+      <c r="AL5" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="AM5" s="24" t="s">
+      <c r="AM5" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="AN5" s="25" t="s">
+      <c r="AN5" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="AO5" s="30" t="s">
+      <c r="AO5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="AP5" s="25" t="s">
+      <c r="AP5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="30" t="s">
+      <c r="AQ5" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="AR5" s="25" t="s">
+      <c r="AR5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="AS5" s="30" t="s">
+      <c r="AS5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="AT5" s="25" t="s">
+      <c r="AT5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AU5" s="26" t="s">
+      <c r="AU5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="AV5" s="14" t="s">
+      <c r="AV5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="AW5" s="15" t="s">
+      <c r="AW5" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AX5" s="16" t="s">
+      <c r="AX5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AY5" s="16" t="s">
+      <c r="AY5" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AZ5" s="16" t="s">
+      <c r="AZ5" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="BA5" s="16" t="s">
+      <c r="BA5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="BB5" s="16" t="s">
+      <c r="BB5" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="BC5" s="16" t="s">
+      <c r="BC5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="BD5" s="16" t="s">
+      <c r="BD5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="BE5" s="16" t="s">
+      <c r="BE5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="BF5" s="16" t="s">
+      <c r="BF5" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="BG5" s="17" t="s">
+      <c r="BG5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="BH5" s="18" t="s">
+      <c r="BH5" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="BI5" s="19" t="s">
+      <c r="BI5" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="BJ5" s="18" t="s">
+      <c r="BJ5" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="BK5" s="18" t="s">
+      <c r="BK5" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="BL5" s="20" t="s">
+      <c r="BL5" s="14" t="s">
         <v>60</v>
       </c>
       <c r="BM5"/>
@@ -6785,122 +6802,122 @@
       <c r="BU5"/>
       <c r="BV5"/>
     </row>
-    <row r="6" spans="1:74" s="22" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:74" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="49" t="e">
+      <c r="B6" s="98"/>
+      <c r="C6" s="99" t="e">
         <f>IFERROR(IF(DAY(DATE(Logbook[[#This Row],[Year]],IF(ISNUMBER(Logbook[[#This Row],[Month]]),MONTH(Logbook[[#This Row],[Month]]),MONTH(DATEVALUE(Logbook[[#This Row],[Month]]&amp;" 1"))),IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]]))))&lt;&gt;IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]])),NA(),DATE(Logbook[[#This Row],[Year]],IF(ISNUMBER(Logbook[[#This Row],[Month]]),MONTH(Logbook[[#This Row],[Month]]),MONTH(DATEVALUE(Logbook[[#This Row],[Month]]&amp;" 1"))),IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]])))),NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="35"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="35"/>
-      <c r="AC6" s="35"/>
-      <c r="AD6" s="35"/>
-      <c r="AE6" s="35"/>
-      <c r="AF6" s="35"/>
-      <c r="AG6" s="35"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="35"/>
-      <c r="AJ6" s="35"/>
-      <c r="AK6" s="35"/>
-      <c r="AL6" s="35"/>
-      <c r="AM6" s="32"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="32"/>
-      <c r="AP6" s="32"/>
-      <c r="AQ6" s="32"/>
-      <c r="AR6" s="32"/>
-      <c r="AS6" s="32"/>
-      <c r="AT6" s="32"/>
-      <c r="AU6" s="37"/>
-      <c r="AV6" s="29">
+      <c r="D6" s="23"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="26"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="25"/>
+      <c r="AK6" s="25"/>
+      <c r="AL6" s="25"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="23"/>
+      <c r="AP6" s="23"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="23"/>
+      <c r="AS6" s="23"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="20">
         <f>SUM(Logbook[[#This Row],[SeIcusDay]:[CopilotNight]])</f>
         <v>0</v>
       </c>
-      <c r="AW6" s="4">
+      <c r="AW6" s="102">
         <f>SUM(Logbook[[#This Row],[ILS]:[DGA (Azi)]])</f>
         <v>0</v>
       </c>
-      <c r="AX6" s="27">
+      <c r="AX6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumLandingsDay]),Logbook[[#This Row],[LandingsDay]],Logbook[[#This Row],[LandingsDay]]+INDEX(Logbook[CumLandingsDay],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AY6" s="27">
+      <c r="AY6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumLandingsNight]),Logbook[[#This Row],[LandingsNight]],Logbook[[#This Row],[LandingsNight]]+INDEX(Logbook[CumLandingsNight],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AZ6" s="27">
+      <c r="AZ6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumILS]),Logbook[[#This Row],[ILS]],Logbook[[#This Row],[ILS]]+INDEX(Logbook[CumILS],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BA6" s="27">
+      <c r="BA6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumVOR]),Logbook[[#This Row],[VOR]],Logbook[[#This Row],[VOR]]+INDEX(Logbook[CumVOR],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BB6" s="27">
+      <c r="BB6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumRNP]),Logbook[[#This Row],[RNP]],Logbook[[#This Row],[RNP]]+INDEX(Logbook[CumRNP],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BC6" s="27">
+      <c r="BC6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumNDB]),Logbook[[#This Row],[NDB]],Logbook[[#This Row],[NDB]]+INDEX(Logbook[CumNDB],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BD6" s="27">
+      <c r="BD6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumDgaCdi]),Logbook[[#This Row],[DGA (CDI)]],Logbook[[#This Row],[DGA (CDI)]]+INDEX(Logbook[CumDgaCdi],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BE6" s="27">
+      <c r="BE6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumDgaAzi]),Logbook[[#This Row],[DGA (Azi)]],Logbook[[#This Row],[DGA (Azi)]]+INDEX(Logbook[CumDgaAzi],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BF6" s="27">
+      <c r="BF6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumCirc]),Logbook[[#This Row],[Circling]],Logbook[[#This Row],[Circling]]+INDEX(Logbook[CumCirc],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BG6" s="27">
+      <c r="BG6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumTotalApps]),Logbook[[#This Row],[TotalApps]],Logbook[[#This Row],[TotalApps]]+INDEX(Logbook[CumTotalApps],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BH6" s="5">
+      <c r="BH6" s="25">
         <f>SUM(INDEX(Logbook[TotalHours],1):Logbook[[#This Row],[TotalHours]])</f>
         <v>0</v>
       </c>
-      <c r="BI6" s="28">
+      <c r="BI6" s="104">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[Cum2D]),SUM(Logbook[[#This Row],[VOR]:[DGA (Azi)]]),SUM(Logbook[[#This Row],[VOR]:[DGA (Azi)]])+INDEX(Logbook[Cum2D],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BJ6" s="27">
+      <c r="BJ6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[Cum3D]),Logbook[[#This Row],[ILS]],Logbook[[#This Row],[ILS]]+INDEX(Logbook[Cum3D],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BK6" s="28">
+      <c r="BK6" s="104">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumCDI]),SUM(Logbook[[#This Row],[ILS]:[RNP]])+Logbook[[#This Row],[DGA (CDI)]],SUM(Logbook[[#This Row],[ILS]:[RNP]])+Logbook[[#This Row],[DGA (CDI)]]+INDEX(Logbook[CumCDI],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BL6" s="6">
+      <c r="BL6" s="105">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumAzi]),Logbook[[#This Row],[NDB]]+Logbook[[#This Row],[DGA (Azi)]],Logbook[[#This Row],[NDB]]+Logbook[[#This Row],[DGA (Azi)]]+INDEX(Logbook[CumAzi],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
@@ -6915,171 +6932,171 @@
       <c r="BU6"/>
       <c r="BV6"/>
     </row>
-    <row r="7" spans="1:74" s="22" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:74" s="15" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="57" t="s">
+      <c r="B7" s="106"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="58">
+      <c r="K7" s="49">
         <f>SUBTOTAL(109,Logbook[TotalHours])</f>
         <v>0</v>
       </c>
-      <c r="L7" s="59"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="60" t="s">
+      <c r="L7" s="50"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="S7" s="62">
+      <c r="S7" s="53">
         <f>SUBTOTAL(109,Logbook[Custom 1])</f>
         <v>0</v>
       </c>
-      <c r="T7" s="62">
+      <c r="T7" s="53">
         <f>SUBTOTAL(109,Logbook[Custom 2])</f>
         <v>0</v>
       </c>
-      <c r="U7" s="62">
+      <c r="U7" s="53">
         <f>SUBTOTAL(109,Logbook[Custom 3])</f>
         <v>0</v>
       </c>
-      <c r="V7" s="63">
+      <c r="V7" s="54">
         <f>SUBTOTAL(109,Logbook[Custom 4])</f>
         <v>0</v>
       </c>
-      <c r="W7" s="62">
+      <c r="W7" s="53">
         <f>SUBTOTAL(109,Logbook[SeIcusDay])</f>
         <v>0</v>
       </c>
-      <c r="X7" s="62">
+      <c r="X7" s="53">
         <f>SUBTOTAL(109,Logbook[SeIcusNight])</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="62">
+      <c r="Y7" s="53">
         <f>SUBTOTAL(109,Logbook[SeDualDay])</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="62">
+      <c r="Z7" s="53">
         <f>SUBTOTAL(109,Logbook[SeDualNight])</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="62">
+      <c r="AA7" s="53">
         <f>SUBTOTAL(109,Logbook[SeCommandDay])</f>
         <v>0</v>
       </c>
-      <c r="AB7" s="62">
+      <c r="AB7" s="53">
         <f>SUBTOTAL(109,Logbook[SeCommandNight])</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="62">
+      <c r="AC7" s="53">
         <f>SUBTOTAL(109,Logbook[MeIcusDay])</f>
         <v>0</v>
       </c>
-      <c r="AD7" s="62">
+      <c r="AD7" s="53">
         <f>SUBTOTAL(109,Logbook[MeIcusNight])</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="62">
+      <c r="AE7" s="53">
         <f>SUBTOTAL(109,Logbook[MeDualDay])</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="62">
+      <c r="AF7" s="53">
         <f>SUBTOTAL(109,Logbook[MeDualNight])</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="62">
+      <c r="AG7" s="53">
         <f>SUBTOTAL(109,Logbook[MeCommandDay])</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="62">
+      <c r="AH7" s="53">
         <f>SUBTOTAL(109,Logbook[MeCommandNight])</f>
         <v>0</v>
       </c>
-      <c r="AI7" s="62">
+      <c r="AI7" s="53">
         <f>SUBTOTAL(109,Logbook[CopilotDay])</f>
         <v>0</v>
       </c>
-      <c r="AJ7" s="62">
+      <c r="AJ7" s="53">
         <f>SUBTOTAL(109,Logbook[CopilotNight])</f>
         <v>0</v>
       </c>
-      <c r="AK7" s="62">
+      <c r="AK7" s="53">
         <f>SUBTOTAL(109,Logbook[IfrIf])</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="62">
+      <c r="AL7" s="53">
         <f>SUBTOTAL(109,Logbook[IfrSim])</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="63">
+      <c r="AM7" s="54">
         <f>SUBTOTAL(109,Logbook[LandingsDay])</f>
         <v>0</v>
       </c>
-      <c r="AN7" s="63">
+      <c r="AN7" s="54">
         <f>SUBTOTAL(109,Logbook[LandingsNight])</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="63">
+      <c r="AO7" s="54">
         <f>SUBTOTAL(109,Logbook[ILS])</f>
         <v>0</v>
       </c>
-      <c r="AP7" s="63">
+      <c r="AP7" s="54">
         <f>SUBTOTAL(109,Logbook[VOR])</f>
         <v>0</v>
       </c>
-      <c r="AQ7" s="63">
+      <c r="AQ7" s="54">
         <f>SUBTOTAL(109,Logbook[RNP])</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="63">
+      <c r="AR7" s="54">
         <f>SUBTOTAL(109,Logbook[NDB])</f>
         <v>0</v>
       </c>
-      <c r="AS7" s="63">
+      <c r="AS7" s="54">
         <f>SUBTOTAL(109,Logbook[DGA (CDI)])</f>
         <v>0</v>
       </c>
-      <c r="AT7" s="63">
+      <c r="AT7" s="54">
         <f>SUBTOTAL(109,Logbook[DGA (Azi)])</f>
         <v>0</v>
       </c>
-      <c r="AU7" s="63">
+      <c r="AU7" s="54">
         <f>SUBTOTAL(109,Logbook[Circling])</f>
         <v>0</v>
       </c>
-      <c r="AV7" s="64">
+      <c r="AV7" s="55">
         <f>SUBTOTAL(109,Logbook[TotalHours])</f>
         <v>0</v>
       </c>
-      <c r="AW7" s="65">
+      <c r="AW7" s="107">
         <f>SUBTOTAL(109,Logbook[TotalApps])</f>
         <v>0</v>
       </c>
-      <c r="AX7" s="66"/>
-      <c r="AY7" s="66"/>
-      <c r="AZ7" s="66"/>
-      <c r="BA7" s="66"/>
-      <c r="BB7" s="66"/>
-      <c r="BC7" s="66"/>
-      <c r="BD7" s="66"/>
-      <c r="BE7" s="66"/>
-      <c r="BF7" s="66"/>
-      <c r="BG7" s="67"/>
-      <c r="BH7" s="66"/>
-      <c r="BI7" s="66"/>
-      <c r="BJ7" s="66"/>
-      <c r="BK7" s="66"/>
-      <c r="BL7" s="68"/>
+      <c r="AX7" s="108"/>
+      <c r="AY7" s="108"/>
+      <c r="AZ7" s="108"/>
+      <c r="BA7" s="108"/>
+      <c r="BB7" s="108"/>
+      <c r="BC7" s="108"/>
+      <c r="BD7" s="108"/>
+      <c r="BE7" s="108"/>
+      <c r="BF7" s="108"/>
+      <c r="BG7" s="109"/>
+      <c r="BH7" s="108"/>
+      <c r="BI7" s="108"/>
+      <c r="BJ7" s="108"/>
+      <c r="BK7" s="108"/>
+      <c r="BL7" s="110"/>
       <c r="BM7"/>
       <c r="BN7"/>
       <c r="BO7"/>
@@ -7091,76 +7108,76 @@
       <c r="BU7"/>
       <c r="BV7"/>
     </row>
-    <row r="8" spans="1:74" s="45" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:74" s="37" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72" t="s">
+      <c r="B8" s="111"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="73">
+      <c r="K8" s="59">
         <f>SUBTOTAL(109,Logbook[TotalHours])+SUBTOTAL(109,Logbook[IfrSim])</f>
         <v>0</v>
       </c>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="74"/>
-      <c r="T8" s="74"/>
-      <c r="U8" s="75"/>
-      <c r="V8" s="75"/>
-      <c r="W8" s="76"/>
-      <c r="X8" s="76"/>
-      <c r="Y8" s="76"/>
-      <c r="Z8" s="76"/>
-      <c r="AA8" s="76"/>
-      <c r="AB8" s="76"/>
-      <c r="AC8" s="76"/>
-      <c r="AD8" s="76"/>
-      <c r="AE8" s="76"/>
-      <c r="AF8" s="76"/>
-      <c r="AG8" s="76"/>
-      <c r="AH8" s="76"/>
-      <c r="AI8" s="76"/>
-      <c r="AJ8" s="76"/>
-      <c r="AK8" s="76"/>
-      <c r="AL8" s="76"/>
-      <c r="AM8" s="38"/>
-      <c r="AN8" s="38"/>
-      <c r="AO8" s="38"/>
-      <c r="AP8" s="38"/>
-      <c r="AQ8" s="38"/>
-      <c r="AR8" s="38"/>
-      <c r="AS8" s="38"/>
-      <c r="AT8" s="38"/>
-      <c r="AU8" s="38"/>
-      <c r="AV8" s="77"/>
-      <c r="AW8" s="78"/>
-      <c r="AX8" s="79"/>
-      <c r="AY8" s="79"/>
-      <c r="AZ8" s="79"/>
-      <c r="BA8" s="79"/>
-      <c r="BB8" s="79"/>
-      <c r="BC8" s="79"/>
-      <c r="BD8" s="79"/>
-      <c r="BE8" s="79"/>
-      <c r="BF8" s="79"/>
-      <c r="BG8" s="79"/>
-      <c r="BH8" s="79"/>
-      <c r="BI8" s="79"/>
-      <c r="BJ8" s="79"/>
-      <c r="BK8" s="80"/>
-      <c r="BL8" s="79"/>
+      <c r="L8" s="116"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="116"/>
+      <c r="O8" s="116"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="116"/>
+      <c r="S8" s="117"/>
+      <c r="T8" s="117"/>
+      <c r="U8" s="118"/>
+      <c r="V8" s="118"/>
+      <c r="W8" s="119"/>
+      <c r="X8" s="119"/>
+      <c r="Y8" s="119"/>
+      <c r="Z8" s="119"/>
+      <c r="AA8" s="119"/>
+      <c r="AB8" s="119"/>
+      <c r="AC8" s="119"/>
+      <c r="AD8" s="119"/>
+      <c r="AE8" s="119"/>
+      <c r="AF8" s="119"/>
+      <c r="AG8" s="119"/>
+      <c r="AH8" s="119"/>
+      <c r="AI8" s="119"/>
+      <c r="AJ8" s="119"/>
+      <c r="AK8" s="119"/>
+      <c r="AL8" s="119"/>
+      <c r="AM8" s="111"/>
+      <c r="AN8" s="111"/>
+      <c r="AO8" s="111"/>
+      <c r="AP8" s="111"/>
+      <c r="AQ8" s="111"/>
+      <c r="AR8" s="111"/>
+      <c r="AS8" s="111"/>
+      <c r="AT8" s="111"/>
+      <c r="AU8" s="111"/>
+      <c r="AV8" s="29"/>
+      <c r="AW8" s="120"/>
+      <c r="AX8" s="28"/>
+      <c r="AY8" s="28"/>
+      <c r="AZ8" s="28"/>
+      <c r="BA8" s="28"/>
+      <c r="BB8" s="28"/>
+      <c r="BC8" s="28"/>
+      <c r="BD8" s="28"/>
+      <c r="BE8" s="28"/>
+      <c r="BF8" s="28"/>
+      <c r="BG8" s="28"/>
+      <c r="BH8" s="28"/>
+      <c r="BI8" s="28"/>
+      <c r="BJ8" s="28"/>
+      <c r="BK8" s="121"/>
+      <c r="BL8" s="28"/>
       <c r="BM8"/>
       <c r="BN8"/>
       <c r="BO8"/>
@@ -7552,7 +7569,7 @@
       <c r="BU13"/>
       <c r="BV13"/>
     </row>
-    <row r="14" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="B14"/>
       <c r="C14"/>
@@ -7628,7 +7645,7 @@
       <c r="BU14"/>
       <c r="BV14"/>
     </row>
-    <row r="15" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
@@ -7704,7 +7721,7 @@
       <c r="BU15"/>
       <c r="BV15"/>
     </row>
-    <row r="16" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
@@ -7780,7 +7797,7 @@
       <c r="BU16"/>
       <c r="BV16"/>
     </row>
-    <row r="17" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
@@ -7856,7 +7873,7 @@
       <c r="BU17"/>
       <c r="BV17"/>
     </row>
-    <row r="18" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
@@ -7932,7 +7949,7 @@
       <c r="BU18"/>
       <c r="BV18"/>
     </row>
-    <row r="19" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
@@ -8008,7 +8025,7 @@
       <c r="BU19"/>
       <c r="BV19"/>
     </row>
-    <row r="20" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
@@ -8084,7 +8101,7 @@
       <c r="BU20"/>
       <c r="BV20"/>
     </row>
-    <row r="21" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
@@ -8160,7 +8177,7 @@
       <c r="BU21"/>
       <c r="BV21"/>
     </row>
-    <row r="22" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -8236,7 +8253,7 @@
       <c r="BU22"/>
       <c r="BV22"/>
     </row>
-    <row r="23" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -8312,7 +8329,7 @@
       <c r="BU23"/>
       <c r="BV23"/>
     </row>
-    <row r="24" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
@@ -8388,7 +8405,7 @@
       <c r="BU24"/>
       <c r="BV24"/>
     </row>
-    <row r="25" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -8464,7 +8481,7 @@
       <c r="BU25"/>
       <c r="BV25"/>
     </row>
-    <row r="26" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26"/>
@@ -8540,7 +8557,7 @@
       <c r="BU26"/>
       <c r="BV26"/>
     </row>
-    <row r="27" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -8616,7 +8633,7 @@
       <c r="BU27"/>
       <c r="BV27"/>
     </row>
-    <row r="28" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
@@ -8692,7 +8709,7 @@
       <c r="BU28"/>
       <c r="BV28"/>
     </row>
-    <row r="29" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
@@ -8768,7 +8785,7 @@
       <c r="BU29"/>
       <c r="BV29"/>
     </row>
-    <row r="30" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
@@ -8844,7 +8861,7 @@
       <c r="BU30"/>
       <c r="BV30"/>
     </row>
-    <row r="31" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
@@ -8920,7 +8937,7 @@
       <c r="BU31"/>
       <c r="BV31"/>
     </row>
-    <row r="32" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
@@ -8996,7 +9013,7 @@
       <c r="BU32"/>
       <c r="BV32"/>
     </row>
-    <row r="33" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33"/>
@@ -9072,7 +9089,7 @@
       <c r="BU33"/>
       <c r="BV33"/>
     </row>
-    <row r="34" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="B34"/>
       <c r="C34"/>
@@ -9148,7 +9165,7 @@
       <c r="BU34"/>
       <c r="BV34"/>
     </row>
-    <row r="35" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
@@ -9224,7 +9241,7 @@
       <c r="BU35"/>
       <c r="BV35"/>
     </row>
-    <row r="36" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="B36"/>
       <c r="C36"/>
@@ -9300,7 +9317,7 @@
       <c r="BU36"/>
       <c r="BV36"/>
     </row>
-    <row r="37" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="B37"/>
       <c r="C37"/>
@@ -9376,7 +9393,7 @@
       <c r="BU37"/>
       <c r="BV37"/>
     </row>
-    <row r="38" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="B38"/>
       <c r="C38"/>
@@ -9452,7 +9469,7 @@
       <c r="BU38"/>
       <c r="BV38"/>
     </row>
-    <row r="39" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="B39"/>
       <c r="C39"/>
@@ -9528,7 +9545,7 @@
       <c r="BU39"/>
       <c r="BV39"/>
     </row>
-    <row r="40" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40"/>
@@ -9604,7 +9621,7 @@
       <c r="BU40"/>
       <c r="BV40"/>
     </row>
-    <row r="41" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41"/>
@@ -9680,7 +9697,7 @@
       <c r="BU41"/>
       <c r="BV41"/>
     </row>
-    <row r="42" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
@@ -9756,7 +9773,7 @@
       <c r="BU42"/>
       <c r="BV42"/>
     </row>
-    <row r="43" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
@@ -9832,7 +9849,7 @@
       <c r="BU43"/>
       <c r="BV43"/>
     </row>
-    <row r="44" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44"/>
@@ -9908,7 +9925,7 @@
       <c r="BU44"/>
       <c r="BV44"/>
     </row>
-    <row r="45" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45"/>
@@ -9984,7 +10001,7 @@
       <c r="BU45"/>
       <c r="BV45"/>
     </row>
-    <row r="46" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
@@ -10060,7 +10077,7 @@
       <c r="BU46"/>
       <c r="BV46"/>
     </row>
-    <row r="47" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47"/>
@@ -10136,7 +10153,7 @@
       <c r="BU47"/>
       <c r="BV47"/>
     </row>
-    <row r="48" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48"/>
@@ -10212,7 +10229,7 @@
       <c r="BU48"/>
       <c r="BV48"/>
     </row>
-    <row r="49" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
@@ -10288,7 +10305,7 @@
       <c r="BU49"/>
       <c r="BV49"/>
     </row>
-    <row r="50" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50"/>
@@ -10364,7 +10381,7 @@
       <c r="BU50"/>
       <c r="BV50"/>
     </row>
-    <row r="51" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51"/>
@@ -10440,7 +10457,7 @@
       <c r="BU51"/>
       <c r="BV51"/>
     </row>
-    <row r="52" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52"/>
@@ -10516,7 +10533,7 @@
       <c r="BU52"/>
       <c r="BV52"/>
     </row>
-    <row r="53" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53"/>
@@ -10592,7 +10609,7 @@
       <c r="BU53"/>
       <c r="BV53"/>
     </row>
-    <row r="54" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54"/>
@@ -10668,7 +10685,7 @@
       <c r="BU54"/>
       <c r="BV54"/>
     </row>
-    <row r="55" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55"/>
@@ -10744,7 +10761,7 @@
       <c r="BU55"/>
       <c r="BV55"/>
     </row>
-    <row r="56" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56"/>
@@ -10820,7 +10837,7 @@
       <c r="BU56"/>
       <c r="BV56"/>
     </row>
-    <row r="57" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -10896,7 +10913,7 @@
       <c r="BU57"/>
       <c r="BV57"/>
     </row>
-    <row r="58" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58"/>
@@ -10972,7 +10989,7 @@
       <c r="BU58"/>
       <c r="BV58"/>
     </row>
-    <row r="59" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="B59"/>
       <c r="C59"/>
@@ -11048,7 +11065,7 @@
       <c r="BU59"/>
       <c r="BV59"/>
     </row>
-    <row r="60" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60"/>
@@ -11124,7 +11141,7 @@
       <c r="BU60"/>
       <c r="BV60"/>
     </row>
-    <row r="61" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61"/>
@@ -11200,7 +11217,7 @@
       <c r="BU61"/>
       <c r="BV61"/>
     </row>
-    <row r="62" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A62"/>
       <c r="B62"/>
       <c r="C62"/>
@@ -11276,7 +11293,7 @@
       <c r="BU62"/>
       <c r="BV62"/>
     </row>
-    <row r="63" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="B63"/>
       <c r="C63"/>
@@ -11352,7 +11369,7 @@
       <c r="BU63"/>
       <c r="BV63"/>
     </row>
-    <row r="64" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
@@ -11428,7 +11445,7 @@
       <c r="BU64"/>
       <c r="BV64"/>
     </row>
-    <row r="65" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="B65"/>
       <c r="C65"/>
@@ -11504,7 +11521,7 @@
       <c r="BU65"/>
       <c r="BV65"/>
     </row>
-    <row r="66" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="B66"/>
       <c r="C66"/>
@@ -11580,7 +11597,7 @@
       <c r="BU66"/>
       <c r="BV66"/>
     </row>
-    <row r="67" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="B67"/>
       <c r="C67"/>
@@ -11656,7 +11673,7 @@
       <c r="BU67"/>
       <c r="BV67"/>
     </row>
-    <row r="68" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
@@ -11732,7 +11749,7 @@
       <c r="BU68"/>
       <c r="BV68"/>
     </row>
-    <row r="69" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="B69"/>
       <c r="C69"/>
@@ -11808,7 +11825,7 @@
       <c r="BU69"/>
       <c r="BV69"/>
     </row>
-    <row r="70" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="B70"/>
       <c r="C70"/>
@@ -11884,7 +11901,7 @@
       <c r="BU70"/>
       <c r="BV70"/>
     </row>
-    <row r="71" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="B71"/>
       <c r="C71"/>
@@ -11960,7 +11977,7 @@
       <c r="BU71"/>
       <c r="BV71"/>
     </row>
-    <row r="72" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="B72"/>
       <c r="C72"/>
@@ -12036,7 +12053,7 @@
       <c r="BU72"/>
       <c r="BV72"/>
     </row>
-    <row r="73" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="B73"/>
       <c r="C73"/>
@@ -12112,7 +12129,7 @@
       <c r="BU73"/>
       <c r="BV73"/>
     </row>
-    <row r="74" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="B74"/>
       <c r="C74"/>
@@ -12188,7 +12205,7 @@
       <c r="BU74"/>
       <c r="BV74"/>
     </row>
-    <row r="75" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="B75"/>
       <c r="C75"/>
@@ -12264,7 +12281,7 @@
       <c r="BU75"/>
       <c r="BV75"/>
     </row>
-    <row r="76" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="B76"/>
       <c r="C76"/>
@@ -12340,7 +12357,7 @@
       <c r="BU76"/>
       <c r="BV76"/>
     </row>
-    <row r="77" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="B77"/>
       <c r="C77"/>
@@ -12416,7 +12433,7 @@
       <c r="BU77"/>
       <c r="BV77"/>
     </row>
-    <row r="78" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A78"/>
       <c r="B78"/>
       <c r="C78"/>
@@ -12492,7 +12509,7 @@
       <c r="BU78"/>
       <c r="BV78"/>
     </row>
-    <row r="79" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A79"/>
       <c r="B79"/>
       <c r="C79"/>
@@ -12568,7 +12585,7 @@
       <c r="BU79"/>
       <c r="BV79"/>
     </row>
-    <row r="80" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A80"/>
       <c r="B80"/>
       <c r="C80"/>
@@ -12644,7 +12661,7 @@
       <c r="BU80"/>
       <c r="BV80"/>
     </row>
-    <row r="81" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="B81"/>
       <c r="C81"/>
@@ -12720,7 +12737,7 @@
       <c r="BU81"/>
       <c r="BV81"/>
     </row>
-    <row r="82" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="B82"/>
       <c r="C82"/>
@@ -12796,7 +12813,7 @@
       <c r="BU82"/>
       <c r="BV82"/>
     </row>
-    <row r="83" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="B83"/>
       <c r="C83"/>
@@ -12872,7 +12889,7 @@
       <c r="BU83"/>
       <c r="BV83"/>
     </row>
-    <row r="84" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="B84"/>
       <c r="C84"/>
@@ -12948,7 +12965,7 @@
       <c r="BU84"/>
       <c r="BV84"/>
     </row>
-    <row r="85" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="B85"/>
       <c r="C85"/>
@@ -13024,7 +13041,7 @@
       <c r="BU85"/>
       <c r="BV85"/>
     </row>
-    <row r="86" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="B86"/>
       <c r="C86"/>
@@ -13100,7 +13117,7 @@
       <c r="BU86"/>
       <c r="BV86"/>
     </row>
-    <row r="87" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="B87"/>
       <c r="C87"/>
@@ -13176,7 +13193,7 @@
       <c r="BU87"/>
       <c r="BV87"/>
     </row>
-    <row r="88" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A88"/>
       <c r="B88"/>
       <c r="C88"/>
@@ -13252,7 +13269,7 @@
       <c r="BU88"/>
       <c r="BV88"/>
     </row>
-    <row r="89" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="B89"/>
       <c r="C89"/>
@@ -13328,7 +13345,7 @@
       <c r="BU89"/>
       <c r="BV89"/>
     </row>
-    <row r="90" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="B90"/>
       <c r="C90"/>
@@ -13404,7 +13421,7 @@
       <c r="BU90"/>
       <c r="BV90"/>
     </row>
-    <row r="91" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="B91"/>
       <c r="C91"/>
@@ -13480,7 +13497,7 @@
       <c r="BU91"/>
       <c r="BV91"/>
     </row>
-    <row r="92" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="B92"/>
       <c r="C92"/>
@@ -13556,7 +13573,7 @@
       <c r="BU92"/>
       <c r="BV92"/>
     </row>
-    <row r="93" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="B93"/>
       <c r="C93"/>
@@ -13632,7 +13649,7 @@
       <c r="BU93"/>
       <c r="BV93"/>
     </row>
-    <row r="94" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="B94"/>
       <c r="C94"/>
@@ -13708,7 +13725,7 @@
       <c r="BU94"/>
       <c r="BV94"/>
     </row>
-    <row r="95" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="B95"/>
       <c r="C95"/>
@@ -13784,7 +13801,7 @@
       <c r="BU95"/>
       <c r="BV95"/>
     </row>
-    <row r="96" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="B96"/>
       <c r="C96"/>
@@ -13860,7 +13877,7 @@
       <c r="BU96"/>
       <c r="BV96"/>
     </row>
-    <row r="97" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -13936,7 +13953,7 @@
       <c r="BU97"/>
       <c r="BV97"/>
     </row>
-    <row r="98" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
@@ -14012,7 +14029,7 @@
       <c r="BU98"/>
       <c r="BV98"/>
     </row>
-    <row r="99" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -14088,7 +14105,7 @@
       <c r="BU99"/>
       <c r="BV99"/>
     </row>
-    <row r="100" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -14164,7 +14181,7 @@
       <c r="BU100"/>
       <c r="BV100"/>
     </row>
-    <row r="101" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -14240,7 +14257,7 @@
       <c r="BU101"/>
       <c r="BV101"/>
     </row>
-    <row r="102" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
@@ -14316,7 +14333,7 @@
       <c r="BU102"/>
       <c r="BV102"/>
     </row>
-    <row r="103" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
@@ -14392,7 +14409,7 @@
       <c r="BU103"/>
       <c r="BV103"/>
     </row>
-    <row r="104" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A104"/>
       <c r="B104"/>
       <c r="C104"/>
